--- a/out/Attention-S4_repeat_5_000008.xlsx
+++ b/out/Attention-S4_repeat_5_000008.xlsx
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC45" t="n">
-        <v>-9.315708769287449e-05</v>
+        <v>-0.000145953157874872</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1070196012911481</v>
+        <v>-0.1676721455103643</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1678180986682392</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1678180986682392</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1678180986682392</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1678180986682392</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1678180986682392</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1678180986682392</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1678180986682392</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1678180986682392</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1678180986682392</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1678180986682392</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1678180986682392</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1678180986682392</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1678180986682392</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.107195290178011</v>
+        <v>-0.1679436076663883</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.2967655539730406</v>
+        <v>0.4513017738485292</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4869056184988809</v>
+        <v>0.7355264559625644</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0211444468266281</v>
+        <v>0.03215515663322779</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2319529869918532</v>
+        <v>0.3478110577996848</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.03708028369412986</v>
+        <v>0.05638906047422489</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2849619779636297</v>
+        <v>0.428423548131868</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.04504816554161525</v>
+        <v>0.06850636076752294</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3379744971440681</v>
+        <v>0.5090415870798785</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0119208732929875</v>
+        <v>0.0181283344864152</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3167105636086252</v>
+        <v>0.4767047611824761</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.00662071862793783</v>
+        <v>0.010071155155942</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3180218968864733</v>
+        <v>0.4787015744635686</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01391396089809551</v>
+        <v>0.02116127987702652</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3392374891218566</v>
+        <v>0.5109655291810995</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.005462997413779955</v>
+        <v>0.008310231504543339</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.336238264329596</v>
+        <v>0.5064073575615371</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.003889903535221407</v>
+        <v>0.005916702319050084</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3385515840686287</v>
+        <v>0.5099275804833362</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001528059163496676</v>
+        <v>0.002326499188417886</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.337714767537842</v>
+        <v>0.5086575415255328</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0008643570261933406</v>
+        <v>0.001317532497294125</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3379160715260736</v>
+        <v>0.5089662911737948</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003261721230522456</v>
+        <v>0.0004988043999624587</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3377029962801158</v>
+        <v>0.5086449427332524</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001502354225216803</v>
+        <v>0.000231706495334477</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3376769859358545</v>
+        <v>0.5086080177533611</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>5.232009589913218e-05</v>
+        <v>8.138380649587527e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3376301586008151</v>
+        <v>0.5085396882041699</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.169450130806508e-05</v>
+        <v>2.075723058958612e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3376016502520689</v>
+        <v>0.508498928459448</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>3.58574352986204e-06</v>
+        <v>7.878615294793062e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3375966368485123</v>
+        <v>0.5084939083541129</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-3.767886923740136e-07</v>
+        <v>1.677971888793091e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.337592291222703</v>
+        <v>0.5084898903097692</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-2.211151546177397e-06</v>
+        <v>-1.195152058104458e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3375889408679101</v>
+        <v>0.5084874556395784</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.752393347619798e-06</v>
+        <v>-3.128590021429696e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3375835715409224</v>
+        <v>0.5084819383975887</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.70653621650487e-06</v>
+        <v>-4.413072433009741e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3375775788074921</v>
+        <v>0.5084756144035808</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3375722110189137</v>
+        <v>0.5084702466150024</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3375722477674054</v>
+        <v>0.5084702833634941</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3375723580128809</v>
+        <v>0.5084703936089696</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3375724315098645</v>
+        <v>0.5084704671059532</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3375726152523237</v>
+        <v>0.5084706508484125</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3375741586889802</v>
+        <v>0.5084721942850688</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3375756286286533</v>
+        <v>0.5084736642247419</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3375768780773752</v>
+        <v>0.508474913673464</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3375782377715725</v>
+        <v>0.5084762733676613</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3375760328620633</v>
+        <v>0.508474068458152</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3375756286286533</v>
+        <v>0.5084736642247419</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3375747834133413</v>
+        <v>0.50847281900943</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3375753346407185</v>
+        <v>0.5084733702368073</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3375750039042921</v>
+        <v>0.5084730395003809</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3375747099163576</v>
+        <v>0.5084727455124464</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3375747834133413</v>
+        <v>0.50847281900943</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3375743424314393</v>
+        <v>0.5084723780275281</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3375742321859638</v>
+        <v>0.5084722677820526</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3375741954374721</v>
+        <v>0.5084722310335609</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3375743424314393</v>
+        <v>0.5084723780275281</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3375738647010457</v>
+        <v>0.5084719002971344</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.337574820161833</v>
+        <v>0.5084728557579217</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3375747834133413</v>
+        <v>0.50847281900943</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3375744526769149</v>
+        <v>0.5084724882730036</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3375748936588168</v>
+        <v>0.5084729292549055</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3375742689344557</v>
+        <v>0.5084723045305445</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3375740851919966</v>
+        <v>0.5084721207880852</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3375736809585865</v>
+        <v>0.5084717165546753</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3375728357432745</v>
+        <v>0.5084708713393633</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3375727989947828</v>
+        <v>0.5084708345908716</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3375729459887501</v>
+        <v>0.5084709815848388</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3375728724917665</v>
+        <v>0.5084709080878552</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3375729459887501</v>
+        <v>0.5084709815848388</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.337572982737242</v>
+        <v>0.5084710183333307</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3375728724917665</v>
+        <v>0.5084709080878552</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3375733134736684</v>
+        <v>0.5084713490697571</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3375732032281928</v>
+        <v>0.5084712388242816</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3375731664797009</v>
+        <v>0.5084712020757897</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3375730929827173</v>
+        <v>0.5084711285788061</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3375730562342256</v>
+        <v>0.5084710918303144</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3375728357432745</v>
+        <v>0.5084708713393633</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3375727622462909</v>
+        <v>0.5084707978423797</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3375726887493073</v>
+        <v>0.5084707243453961</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3375727254977992</v>
+        <v>0.508470761093888</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3375726152523237</v>
+        <v>0.5084706508484125</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3375727254977992</v>
+        <v>0.508470761093888</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3375730194857337</v>
+        <v>0.5084710550818224</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_5_000008.xlsx
+++ b/out/Attention-S4_repeat_5_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,17 +36712,17 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC45" t="n">
-        <v>-9.315708769287449e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1070196012911481</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -39892,17 +39892,17 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -40687,17 +40687,17 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -41482,17 +41482,17 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -42277,17 +42277,17 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -43072,17 +43072,17 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -43867,17 +43867,17 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -44662,17 +44662,17 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -45457,17 +45457,17 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -46252,17 +46252,17 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -47047,17 +47047,17 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -47842,17 +47842,17 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.107195290178011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.2967655539730406</v>
+        <v>0</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4869056184988809</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0211444468266281</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2319529869918532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.03708028369412986</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2849619779636297</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.04504816554161525</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3379744971440681</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0119208732929875</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3167105636086252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -52608,21 +52608,21 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.00662071862793783</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3180218968864733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -53403,21 +53403,21 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01391396089809551</v>
+        <v>0</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3392374891218566</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -54198,21 +54198,21 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.005462997413779955</v>
+        <v>0</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.336238264329596</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -54993,21 +54993,21 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.003889903535221407</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3385515840686287</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -55788,21 +55788,21 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001528059163496676</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.337714767537842</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -56583,21 +56583,21 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0008643570261933406</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3379160715260736</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -57378,21 +57378,21 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003261721230522456</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3377029962801158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -58173,21 +58173,21 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001502354225216803</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3376769859358545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -58968,21 +58968,21 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>5.232009589913218e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3376301586008151</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -59763,21 +59763,21 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.169450130806508e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3376016502520689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -60558,21 +60558,21 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>3.58574352986204e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3375966368485123</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -61353,21 +61353,21 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-3.767886923740136e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.337592291222703</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -62148,21 +62148,21 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-2.211151546177397e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3375889408679101</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -62943,21 +62943,21 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.752393347619798e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3375835715409224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -63738,21 +63738,21 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.70653621650487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3375775788074921</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -64533,21 +64533,21 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>-4.890058184668745e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3375722110189137</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3375722477674054</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3375723580128809</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3375724315098645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3375726152523237</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3375741586889802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3375756286286533</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3375768780773752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3375782377715725</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3375760328620633</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3375756286286533</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3375747834133413</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3375753346407185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3375750039042921</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3375747099163576</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3375747834133413</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3375743424314393</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3375742321859638</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3375741954374721</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3375743424314393</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3375738647010457</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.337574820161833</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3375747834133413</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3375744526769149</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3375748936588168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3375742689344557</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3375740851919966</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3375736809585865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3375728357432745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3375727989947828</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3375729459887501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3375728724917665</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3375729459887501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.337572982737242</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3375728724917665</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3375733134736684</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3375732032281928</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3375731664797009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3375730929827173</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3375730562342256</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3375728357432745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3375727622462909</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3375726887493073</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3375727254977992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3375726152523237</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3375727254977992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-4.082561524747701e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell (Force)</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3375730194857337</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_5_000008.xlsx
+++ b/out/Attention-S4_repeat_5_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.01257157325744629</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.01156263053417206</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.01112905144691467</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.01162847876548767</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.008100904524326324</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.00960078090429306</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.009091466665267944</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.007935404777526855</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.009701482951641083</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.008648432791233063</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.008568614721298218</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.006900489330291748</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.008536085486412048</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.009631417691707611</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.0109381228685379</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.008597463369369507</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.01014294475317001</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.009298540651798248</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.009303182363510132</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.009616084396839142</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.009513460099697113</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.009899482131004333</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.009170085191726685</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.009318128228187561</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.008682690560817719</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.01028338074684143</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.01007945090532303</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.01134786009788513</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.01088537275791168</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.01097621023654938</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.01172849535942078</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.006881698966026306</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.01047185063362122</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.00925900787115097</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.00861600786447525</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.01077865064144135</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.008878029882907867</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.00960078090429306</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.0111466571688652</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.01055918633937836</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.01156293600797653</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.01418449729681015</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.01773474738001823</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,17 +36712,17 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.01101049035787582</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>-0.0001196160965063609</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>-0.1374159204966616</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.01295442879199982</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.01875683665275574</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.0142090767621994</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="49">
@@ -39892,17 +39892,17 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.01755476742982864</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="50">
@@ -40687,17 +40687,17 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.01607295498251915</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>0</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="51">
@@ -41482,17 +41482,17 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.01647468656301498</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>0</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="52">
@@ -42277,17 +42277,17 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.01531336829066277</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="53">
@@ -43072,17 +43072,17 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.0164276547729969</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC53" t="n">
-        <v>0</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="54">
@@ -43867,17 +43867,17 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.01501065865159035</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC54" t="n">
-        <v>0</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="55">
@@ -44662,17 +44662,17 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.01567653566598892</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC55" t="n">
-        <v>0</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="56">
@@ -45457,17 +45457,17 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.01491027325391769</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC56" t="n">
-        <v>0</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="57">
@@ -46252,17 +46252,17 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.01483368501067162</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC57" t="n">
-        <v>0</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="58">
@@ -47047,17 +47047,17 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.01694139465689659</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC58" t="n">
-        <v>0</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="59">
@@ -47842,17 +47842,17 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.01788941025733948</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC59" t="n">
-        <v>0</v>
+        <v>-0.1376213479008775</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>0.3085579198048224</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.01263427734375</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0</v>
+        <v>0.4800869342137966</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>0.02198468700253113</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.01689795777201653</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0</v>
+        <v>0.215003427642894</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0</v>
+        <v>0.03855365035540723</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.01604881510138512</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC62" t="n">
-        <v>0</v>
+        <v>0.2701187045506146</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>0.04683782024531166</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.01311025395989418</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC63" t="n">
-        <v>0</v>
+        <v>0.3252376504342635</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>0.01239446076773728</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.01642364263534546</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC64" t="n">
-        <v>0</v>
+        <v>0.3031286582414871</v>
       </c>
     </row>
     <row r="65">
@@ -52608,21 +52608,21 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0</v>
+        <v>0.006884133133743996</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.02245069667696953</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0</v>
+        <v>0.3044923226881102</v>
       </c>
     </row>
     <row r="66">
@@ -53403,21 +53403,21 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0</v>
+        <v>0.01446732822505191</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.0148063637316227</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0</v>
+        <v>0.3265515218388678</v>
       </c>
     </row>
     <row r="67">
@@ -54198,21 +54198,21 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0</v>
+        <v>0.005680990666156564</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.01342254132032394</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0</v>
+        <v>0.3234332698804752</v>
       </c>
     </row>
     <row r="68">
@@ -54993,21 +54993,21 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0</v>
+        <v>0.004043422762251835</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.00999932736158371</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0</v>
+        <v>0.3258384816257511</v>
       </c>
     </row>
     <row r="69">
@@ -55788,21 +55788,21 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0</v>
+        <v>0.001589164267444728</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.01254343241453171</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0</v>
+        <v>0.3249685103173868</v>
       </c>
     </row>
     <row r="70">
@@ -56583,21 +56583,21 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0</v>
+        <v>0.0008998095290345585</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.01035812497138977</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0</v>
+        <v>0.3251780361760189</v>
       </c>
     </row>
     <row r="71">
@@ -57378,21 +57378,21 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0</v>
+        <v>0.0003390901845897445</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.01335200294852257</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0</v>
+        <v>0.3249568588542759</v>
       </c>
     </row>
     <row r="72">
@@ -58173,21 +58173,21 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0</v>
+        <v>0.0001568411851821773</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.01082438230514526</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0</v>
+        <v>0.3249300310773268</v>
       </c>
     </row>
     <row r="73">
@@ -58968,21 +58968,21 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>0</v>
+        <v>5.393474648784013e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.01109113544225693</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0</v>
+        <v>0.3248817315195631</v>
       </c>
     </row>
     <row r="74">
@@ -59763,21 +59763,21 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>0</v>
+        <v>1.264847281138308e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.01236794143915176</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0</v>
+        <v>0.3248522294722537</v>
       </c>
     </row>
     <row r="75">
@@ -60558,21 +60558,21 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>0</v>
+        <v>3.58574352986204e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.01005935668945312</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0</v>
+        <v>0.3248472160686969</v>
       </c>
     </row>
     <row r="76">
@@ -61353,21 +61353,21 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>0</v>
+        <v>-3.767886923740136e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.008898831903934479</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0</v>
+        <v>0.3248429071913795</v>
       </c>
     </row>
     <row r="77">
@@ -62148,21 +62148,21 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>0</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.007573619484901428</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0</v>
+        <v>0.3248397395698147</v>
       </c>
     </row>
     <row r="78">
@@ -62943,21 +62943,21 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>0</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.009903214871883392</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0</v>
+        <v>0.3248343702428269</v>
       </c>
     </row>
     <row r="79">
@@ -63738,21 +63738,21 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>0</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.01190479844808578</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0</v>
+        <v>0.3248283775093965</v>
       </c>
     </row>
     <row r="80">
@@ -64533,21 +64533,21 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>0</v>
+        <v>-4.890058184668745e-06</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.01180953532457352</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0</v>
+        <v>0.3248230097208181</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.01011336594820023</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0</v>
+        <v>0.3248230464693098</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.01074797660112381</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0</v>
+        <v>0.3248231567147854</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.01041804999113083</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC83" t="n">
-        <v>0</v>
+        <v>0.324823230211769</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.01355168968439102</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0</v>
+        <v>0.3248234139542281</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.0184113010764122</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0</v>
+        <v>0.3248249573908846</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.01933133229613304</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0</v>
+        <v>0.3248264273305577</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.03551451116800308</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0</v>
+        <v>0.3248276767792797</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.02598758786916733</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0</v>
+        <v>0.3248290364734771</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.006621792912483215</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>0</v>
+        <v>0.3248268315639677</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.02233529090881348</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0</v>
+        <v>0.3248264273305577</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.01613112539052963</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>0</v>
+        <v>0.3248255821152458</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.01872915029525757</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC92" t="n">
-        <v>0</v>
+        <v>0.324826133342623</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.0230243057012558</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>0</v>
+        <v>0.3248258026061966</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.02770773321390152</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC94" t="n">
-        <v>0</v>
+        <v>0.3248255086182621</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.01124654710292816</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC95" t="n">
-        <v>0</v>
+        <v>0.3248255821152458</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.01885191723704338</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC96" t="n">
-        <v>0</v>
+        <v>0.3248251411333438</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.01700136065483093</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC97" t="n">
-        <v>0</v>
+        <v>0.3248250308878682</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.02128662914037704</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC98" t="n">
-        <v>0</v>
+        <v>0.3248249941393765</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.02094036713242531</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0</v>
+        <v>0.3248251411333438</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.02508514374494553</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0</v>
+        <v>0.3248246634029501</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.031926479190588</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0</v>
+        <v>0.3248256188637375</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.01983089372515678</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0</v>
+        <v>0.3248255821152458</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.01911608502268791</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0</v>
+        <v>0.3248252513788193</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.01716156303882599</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC104" t="n">
-        <v>0</v>
+        <v>0.3248256923607213</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.01700470596551895</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0</v>
+        <v>0.3248250676363602</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.01878451183438301</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0</v>
+        <v>0.324824883893901</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.01454586908221245</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0</v>
+        <v>0.324824479660491</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.01205964386463165</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0</v>
+        <v>0.324823634445179</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.009673707187175751</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0</v>
+        <v>0.3248235976966873</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.01378616690635681</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0</v>
+        <v>0.3248237446906546</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.01539595052599907</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0</v>
+        <v>0.3248236711936709</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.01513726264238358</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0</v>
+        <v>0.3248237446906546</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.009871542453765869</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0</v>
+        <v>0.3248237814391465</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.01567079871892929</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0</v>
+        <v>0.3248236711936709</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.01747819408774376</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0</v>
+        <v>0.3248241121755729</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.009005889296531677</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0</v>
+        <v>0.3248240019300974</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.009227350354194641</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0</v>
+        <v>0.3248239651816054</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.01078758388757706</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0</v>
+        <v>0.3248238916846218</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.008800849318504333</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0</v>
+        <v>0.3248238549361301</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.00783780962228775</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0</v>
+        <v>0.324823634445179</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.008744850754737854</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0</v>
+        <v>0.3248235609481954</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.008121252059936523</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0</v>
+        <v>0.3248234874512118</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.003370590507984161</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0</v>
+        <v>0.3248235241997037</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.006104893982410431</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>0</v>
+        <v>0.3248234139542281</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.01507225632667542</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5800000000000005</v>
       </c>
       <c r="JC125" t="n">
-        <v>0</v>
+        <v>0.3248235241997037</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>-4.082561524747701e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.01622328907251358</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.04000000000000001</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0</v>
+        <v>0.3248238181876382</v>
       </c>
     </row>
   </sheetData>
